--- a/Analysis/Output/bindrows_data_report.xlsx
+++ b/Analysis/Output/bindrows_data_report.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -439,24 +439,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>education</t>
+          <t>date_of_interview</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>factor</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>factor</t>
+          <t>Date</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>gad7_1</t>
+          <t>education</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -473,7 +473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>gad7_2</t>
+          <t>gad7_1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -490,7 +490,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>gad7_3</t>
+          <t>gad7_2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -507,7 +507,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>gad7_4</t>
+          <t>gad7_3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -524,7 +524,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>gad7_5</t>
+          <t>gad7_4</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>gad7_6</t>
+          <t>gad7_5</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -558,7 +558,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>gad7_7</t>
+          <t>gad7_6</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -575,7 +575,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>gad7_anxiety</t>
+          <t>gad7_7</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -592,44 +592,49 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>gad7_total_score</t>
+          <t>gad7_anxiety</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>factor</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>factor</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>h_head</t>
+          <t>gad7_total_score</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>factor</t>
+          <t>numeric</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>factor</t>
+          <t>numeric</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>incomesource</t>
+          <t>h_head</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
+        <is>
+          <t>factor</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
@@ -638,15 +643,10 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>marstat</t>
+          <t>incomesource</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
-        <is>
-          <t>factor</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
@@ -655,10 +655,15 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>mh_services</t>
+          <t>marstat</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
+        <is>
+          <t>factor</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
@@ -667,41 +672,36 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>person_id</t>
+          <t>mh_services</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>numeric</t>
+          <t>factor</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>phq9_1</t>
+          <t>person_id</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>factor</t>
+          <t>numeric</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>factor</t>
+          <t>numeric</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>phq9_2</t>
+          <t>phq9_1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -718,7 +718,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>phq9_3</t>
+          <t>phq9_2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -735,7 +735,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>phq9_4</t>
+          <t>phq9_3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -752,7 +752,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>phq9_5</t>
+          <t>phq9_4</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -769,7 +769,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>phq9_6</t>
+          <t>phq9_5</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -786,7 +786,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>phq9_7</t>
+          <t>phq9_6</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -803,7 +803,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>phq9_8</t>
+          <t>phq9_7</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -820,7 +820,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>phq9_9</t>
+          <t>phq9_8</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -837,7 +837,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>phq9_depression</t>
+          <t>phq9_9</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -854,41 +854,41 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>phq9_totalscore</t>
+          <t>phq9_depression</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>factor</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>factor</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>psq_hallucinations</t>
+          <t>phq9_totalscore</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>factor</t>
+          <t>numeric</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>factor</t>
+          <t>numeric</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>psq_hallucinations2</t>
+          <t>psq_hallucinations</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -905,7 +905,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>psq_hypomania</t>
+          <t>psq_hallucinations2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -922,7 +922,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>psq_hypomania2</t>
+          <t>psq_hypomania</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -939,7 +939,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>psq_paranoia</t>
+          <t>psq_hypomania2</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -956,7 +956,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>psq_paranoia2</t>
+          <t>psq_paranoia</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -973,7 +973,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>psq_psychosis</t>
+          <t>psq_paranoia2</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -990,7 +990,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>psq_strangeexperiences</t>
+          <t>psq_psychosis</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1007,7 +1007,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>psq_strangeexperiences2</t>
+          <t>psq_strangeexperiences</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1024,7 +1024,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>psq_thoughtinsertion</t>
+          <t>psq_strangeexperiences2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1041,7 +1041,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>psq_thoughtinsertion2</t>
+          <t>psq_thoughtinsertion</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1058,41 +1058,41 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>psq_totalscore</t>
+          <t>psq_thoughtinsertion2</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>factor</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>factor</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>psq_totalscore</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>factor</t>
+          <t>numeric</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>factor</t>
+          <t>numeric</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>site</t>
+          <t>sex</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1109,7 +1109,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>social_media</t>
+          <t>site</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1126,10 +1126,15 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>study</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
+        <is>
+          <t>factor</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
@@ -1138,10 +1143,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>study</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>factor</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>supportive</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
@@ -1154,7 +1171,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1240,24 +1257,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>education</t>
+          <t>date_of_interview</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>factor</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>factor</t>
+          <t>Date</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>gad7_1</t>
+          <t>education</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1274,7 +1291,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>gad7_2</t>
+          <t>gad7_1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1291,7 +1308,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>gad7_3</t>
+          <t>gad7_2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1308,7 +1325,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>gad7_4</t>
+          <t>gad7_3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1325,7 +1342,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>gad7_5</t>
+          <t>gad7_4</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1342,7 +1359,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>gad7_6</t>
+          <t>gad7_5</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1359,7 +1376,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>gad7_7</t>
+          <t>gad7_6</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1376,7 +1393,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>gad7_anxiety</t>
+          <t>gad7_7</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1393,44 +1410,49 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>gad7_total_score</t>
+          <t>gad7_anxiety</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>factor</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>factor</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>h_head</t>
+          <t>gad7_total_score</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>factor</t>
+          <t>numeric</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>factor</t>
+          <t>numeric</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>incomesource</t>
+          <t>h_head</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
+        <is>
+          <t>factor</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
@@ -1439,15 +1461,10 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>marstat</t>
+          <t>incomesource</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
-        <is>
-          <t>factor</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
@@ -1456,10 +1473,15 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>mh_services</t>
+          <t>marstat</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
+        <is>
+          <t>factor</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
@@ -1468,41 +1490,36 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>person_id</t>
+          <t>mh_services</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>numeric</t>
+          <t>factor</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>phq9_1</t>
+          <t>person_id</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>factor</t>
+          <t>numeric</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>factor</t>
+          <t>numeric</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>phq9_2</t>
+          <t>phq9_1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1519,7 +1536,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>phq9_3</t>
+          <t>phq9_2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1536,7 +1553,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>phq9_4</t>
+          <t>phq9_3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1553,7 +1570,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>phq9_5</t>
+          <t>phq9_4</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1570,7 +1587,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>phq9_6</t>
+          <t>phq9_5</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1587,7 +1604,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>phq9_7</t>
+          <t>phq9_6</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1604,7 +1621,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>phq9_8</t>
+          <t>phq9_7</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1621,7 +1638,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>phq9_9</t>
+          <t>phq9_8</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1638,7 +1655,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>phq9_depression</t>
+          <t>phq9_9</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1655,41 +1672,41 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>phq9_totalscore</t>
+          <t>phq9_depression</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>factor</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>factor</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>psq_hallucinations</t>
+          <t>phq9_totalscore</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>factor</t>
+          <t>numeric</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>factor</t>
+          <t>numeric</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>psq_hallucinations2</t>
+          <t>psq_hallucinations</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1706,7 +1723,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>psq_hypomania</t>
+          <t>psq_hallucinations2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1723,7 +1740,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>psq_hypomania2</t>
+          <t>psq_hypomania</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1740,7 +1757,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>psq_paranoia</t>
+          <t>psq_hypomania2</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1757,7 +1774,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>psq_paranoia2</t>
+          <t>psq_paranoia</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1774,7 +1791,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>psq_psychosis</t>
+          <t>psq_paranoia2</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1791,7 +1808,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>psq_strangeexperiences</t>
+          <t>psq_psychosis</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1808,7 +1825,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>psq_strangeexperiences2</t>
+          <t>psq_strangeexperiences</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1825,7 +1842,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>psq_thoughtinsertion</t>
+          <t>psq_strangeexperiences2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1842,7 +1859,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>psq_thoughtinsertion2</t>
+          <t>psq_thoughtinsertion</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1859,41 +1876,41 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>psq_totalscore</t>
+          <t>psq_thoughtinsertion2</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>factor</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>factor</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>psq_totalscore</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>factor</t>
+          <t>numeric</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>factor</t>
+          <t>numeric</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>site</t>
+          <t>sex</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1910,7 +1927,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>social_media</t>
+          <t>site</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1927,10 +1944,15 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>study</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
+        <is>
+          <t>factor</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
@@ -1939,10 +1961,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>study</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>factor</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>supportive</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
